--- a/data/trans_dic/P45C_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,51</t>
+          <t>0,71; 3,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,91</t>
+          <t>0,58; 3,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,22</t>
+          <t>0,33; 3,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,09</t>
+          <t>0,31; 2,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,73</t>
+          <t>0,84; 3,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,48</t>
+          <t>0,41; 2,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,67</t>
+          <t>0,77; 2,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,99</t>
+          <t>0,89; 2,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,35</t>
+          <t>0,51; 2,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,2</t>
+          <t>0,71; 2,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,66</t>
+          <t>0,24; 2,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,92</t>
+          <t>0,51; 2,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,13</t>
+          <t>0,48; 3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,97</t>
+          <t>0,35; 4,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,08</t>
+          <t>0,75; 3,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,17</t>
+          <t>1,18; 5,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,26</t>
+          <t>0,94; 4,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,76</t>
+          <t>1,35; 4,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,41</t>
+          <t>0,63; 2,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,21</t>
+          <t>1,09; 3,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,79</t>
+          <t>0,86; 3,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,57</t>
+          <t>1,06; 3,56</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,78</t>
+          <t>1,76; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,73</t>
+          <t>0,66; 2,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,31</t>
+          <t>0,5; 3,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,52</t>
+          <t>1,2; 7,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,57</t>
+          <t>0,76; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,66</t>
+          <t>1,99; 4,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,46</t>
+          <t>0,78; 2,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,06</t>
+          <t>0,48; 2,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,53</t>
+          <t>0,97; 2,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,86</t>
+          <t>0,56; 1,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,34</t>
+          <t>0,35; 1,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,32</t>
+          <t>0,83; 2,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,53</t>
+          <t>1,22; 3,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,4</t>
+          <t>0,64; 2,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,57</t>
+          <t>0,26; 1,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,84</t>
+          <t>0,44; 1,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,57</t>
+          <t>1,23; 2,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,76</t>
+          <t>0,76; 1,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,25</t>
+          <t>0,45; 1,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,89</t>
+          <t>0,73; 1,86</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,11</t>
+          <t>0,53; 3,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,05</t>
+          <t>0,61; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,2</t>
+          <t>0,4; 2,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,42</t>
+          <t>1,05; 4,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,13</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,25</t>
+          <t>0,57; 2,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,02</t>
+          <t>0,44; 2,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,15</t>
+          <t>1,28; 3,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,54</t>
+          <t>0,86; 2,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,16</t>
+          <t>0,84; 2,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,71</t>
+          <t>0,56; 1,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,02</t>
+          <t>1,44; 3,07</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,84</t>
+          <t>0,3; 3,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,38</t>
+          <t>0,71; 5,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,04</t>
+          <t>0,7; 2,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,5</t>
+          <t>0,99; 2,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,95</t>
+          <t>0,56; 1,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,2</t>
+          <t>0,25; 1,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,94</t>
+          <t>0,71; 1,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,27</t>
+          <t>0,93; 2,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,21</t>
+          <t>0,76; 2,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,04</t>
+          <t>0,33; 2,14</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,23</t>
+          <t>1,28; 2,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,73</t>
+          <t>0,94; 1,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,31</t>
+          <t>0,65; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,18</t>
+          <t>1,1; 2,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,16</t>
+          <t>1,26; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,06</t>
+          <t>1,2; 1,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,54</t>
+          <t>0,79; 1,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,8</t>
+          <t>1,02; 1,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,03</t>
+          <t>1,36; 2,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,76</t>
+          <t>1,17; 1,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,29</t>
+          <t>0,8; 1,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,85</t>
+          <t>1,16; 1,84</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3505; 16624</t>
+          <t>3345; 15822</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3922; 18344</t>
+          <t>3931; 18355</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9000</t>
+          <t>0; 9844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2803; 14693</t>
+          <t>2938; 15599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>997; 9850</t>
+          <t>995; 10179</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1046; 9650</t>
+          <t>975; 9194</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2824; 12738</t>
+          <t>2875; 12660</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2088; 11119</t>
+          <t>1849; 11043</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5967; 20815</t>
+          <t>5966; 20452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6705; 22370</t>
+          <t>6688; 21733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3958; 18027</t>
+          <t>3890; 17389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6751; 20976</t>
+          <t>6751; 21079</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>889; 9764</t>
+          <t>892; 9716</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2047; 12036</t>
+          <t>2089; 11930</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1046; 11715</t>
+          <t>1789; 11450</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1563; 17964</t>
+          <t>1569; 19937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1971; 11451</t>
+          <t>2793; 12631</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4088; 17309</t>
+          <t>3954; 16902</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3057; 15717</t>
+          <t>3471; 15696</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4785; 18198</t>
+          <t>5159; 18597</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4690; 17797</t>
+          <t>4665; 17052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7648; 23951</t>
+          <t>8118; 24249</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6435; 20724</t>
+          <t>6411; 22387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8403; 29762</t>
+          <t>8818; 29745</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9218; 25831</t>
+          <t>9516; 27268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3690; 17138</t>
+          <t>4140; 17069</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6520</t>
+          <t>0; 6833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2857; 22082</t>
+          <t>3308; 23394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2049; 12623</t>
+          <t>2014; 12133</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1943; 11686</t>
+          <t>1939; 11323</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>648; 6053</t>
+          <t>649; 6056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14461; 32976</t>
+          <t>14086; 32751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7140; 21784</t>
+          <t>6887; 21963</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7063</t>
+          <t>0; 6508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4568; 25531</t>
+          <t>3976; 24677</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11953; 31305</t>
+          <t>12034; 30106</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6715; 21324</t>
+          <t>6402; 19831</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3864; 15286</t>
+          <t>4000; 15904</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8334; 23910</t>
+          <t>8552; 25664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8813; 25124</t>
+          <t>8683; 26047</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4473; 18270</t>
+          <t>4850; 20375</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2141; 12888</t>
+          <t>2170; 12527</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3865; 17979</t>
+          <t>4349; 18077</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24083; 50056</t>
+          <t>23856; 48930</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14824; 33654</t>
+          <t>14475; 33383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8534; 24418</t>
+          <t>8768; 24243</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14825; 37873</t>
+          <t>14734; 37404</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1795; 10881</t>
+          <t>1838; 10735</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3789; 15484</t>
+          <t>3109; 14679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2454; 13660</t>
+          <t>2489; 14032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5161; 20952</t>
+          <t>4949; 19898</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4029; 17753</t>
+          <t>4170; 18050</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4379; 17043</t>
+          <t>4355; 16843</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3050; 14822</t>
+          <t>3245; 14953</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10438; 26471</t>
+          <t>10754; 26676</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7925; 23279</t>
+          <t>7935; 23965</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10938; 27381</t>
+          <t>10576; 27322</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8341; 23074</t>
+          <t>7551; 24138</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18790; 39721</t>
+          <t>18914; 40401</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>882; 11382</t>
+          <t>882; 10155</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6463</t>
+          <t>0; 6445</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2149; 15189</t>
+          <t>1994; 15123</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 17493</t>
+          <t>0; 17821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9200; 25399</t>
+          <t>8715; 25023</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10828; 27261</t>
+          <t>10777; 28395</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6173; 20951</t>
+          <t>5964; 19759</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1840; 9142</t>
+          <t>1892; 8807</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11855; 29966</t>
+          <t>10914; 28919</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12068; 30820</t>
+          <t>12640; 30975</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11059; 29930</t>
+          <t>10260; 30467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3441; 20378</t>
+          <t>3278; 21419</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>40993; 72829</t>
+          <t>41614; 71779</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31752; 58875</t>
+          <t>32033; 59054</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20409; 44065</t>
+          <t>21782; 45872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37258; 73575</t>
+          <t>37181; 75000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>42501; 72635</t>
+          <t>42381; 73512</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41611; 72248</t>
+          <t>42318; 70126</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28171; 54078</t>
+          <t>27715; 54561</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36507; 64439</t>
+          <t>36399; 65065</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>90401; 134722</t>
+          <t>90524; 133159</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79788; 121313</t>
+          <t>80973; 122999</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54899; 88805</t>
+          <t>54763; 89397</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>80536; 128259</t>
+          <t>80477; 128010</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,34</t>
+          <t>0,59; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,21</t>
+          <t>0,78; 4,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,09</t>
+          <t>0,82; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,33</t>
+          <t>0,37; 3,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,94</t>
+          <t>0,33; 3,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,71</t>
+          <t>0,87; 4,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,47</t>
+          <t>0,37; 2,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,62</t>
+          <t>0,82; 2,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,9</t>
+          <t>0,84; 2,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,27</t>
+          <t>0,52; 2,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,21</t>
+          <t>0,71; 2,32</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,65</t>
+          <t>0,24; 3,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,9</t>
+          <t>0,51; 3,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,06</t>
+          <t>0,28; 3,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,41</t>
+          <t>0,32; 3,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,4</t>
+          <t>0,54; 3,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,05</t>
+          <t>1,16; 5,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,25</t>
+          <t>0,87; 4,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,86</t>
+          <t>1,31; 4,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,31</t>
+          <t>0,6; 2,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,25</t>
+          <t>0,96; 3,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,01</t>
+          <t>0,87; 2,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,56</t>
+          <t>0,97; 3,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,04</t>
+          <t>1,72; 5,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,72</t>
+          <t>0,56; 2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,51</t>
+          <t>1,45; 4,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,23</t>
+          <t>1,23; 7,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,43</t>
+          <t>0,75; 4,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,64</t>
+          <t>0,36; 3,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,62</t>
+          <t>1,96; 4,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,48</t>
+          <t>0,81; 2,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,96</t>
+          <t>1,33; 3,84</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,44</t>
+          <t>1,0; 2,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,73</t>
+          <t>0,59; 1,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,4</t>
+          <t>0,36; 1,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,49</t>
+          <t>0,79; 2,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,66</t>
+          <t>1,32; 3,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,68</t>
+          <t>0,64; 2,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,53</t>
+          <t>0,33; 1,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,85</t>
+          <t>0,8; 2,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,51</t>
+          <t>1,24; 2,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,75</t>
+          <t>0,73; 1,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,24</t>
+          <t>0,43; 1,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,86</t>
+          <t>0,99; 2,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,07</t>
+          <t>0,51; 3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,89</t>
+          <t>0,72; 2,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,26</t>
+          <t>0,38; 2,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,2</t>
+          <t>0,89; 3,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,73; 3,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,22</t>
+          <t>0,56; 2,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,04</t>
+          <t>0,43; 2,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,17</t>
+          <t>1,49; 3,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,61</t>
+          <t>0,79; 2,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,16</t>
+          <t>0,84; 2,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,78</t>
+          <t>0,6; 1,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,07</t>
+          <t>1,47; 3,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,42</t>
+          <t>0,3; 3,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,35</t>
+          <t>0,76; 4,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 6,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,01</t>
+          <t>0,72; 2,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,6</t>
+          <t>1,01; 2,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,84</t>
+          <t>0,61; 2,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,16</t>
+          <t>0,23; 1,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,88</t>
+          <t>0,78; 2,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,28</t>
+          <t>0,93; 2,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,25</t>
+          <t>0,81; 2,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,14</t>
+          <t>0,3; 1,72</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,2</t>
+          <t>1,27; 2,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,74</t>
+          <t>0,97; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,37</t>
+          <t>0,59; 1,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,23</t>
+          <t>1,24; 2,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,18</t>
+          <t>1,26; 2,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,99</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,56</t>
+          <t>0,79; 1,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,82</t>
+          <t>1,13; 1,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,01</t>
+          <t>1,39; 2,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,78</t>
+          <t>1,18; 1,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,3</t>
+          <t>0,81; 1,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,84</t>
+          <t>1,27; 1,88</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>14286</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3345; 15822</t>
+          <t>2801; 15160</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3931; 18355</t>
+          <t>3411; 17631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9844</t>
+          <t>0; 10674</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2938; 15599</t>
+          <t>4542; 18027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>995; 10179</t>
+          <t>1135; 10417</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>975; 9194</t>
+          <t>1041; 10081</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2875; 12660</t>
+          <t>2976; 13708</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1849; 11043</t>
+          <t>1784; 10289</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5966; 20452</t>
+          <t>6356; 20812</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6688; 21733</t>
+          <t>6304; 21775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3890; 17389</t>
+          <t>3983; 16896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6751; 21079</t>
+          <t>7388; 24152</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16209</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>892; 9716</t>
+          <t>892; 11025</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2089; 11930</t>
+          <t>2079; 12691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1789; 11450</t>
+          <t>1049; 12176</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1569; 19937</t>
+          <t>1560; 18474</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2793; 12631</t>
+          <t>2019; 12271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3954; 16902</t>
+          <t>3895; 17202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3471; 15696</t>
+          <t>3227; 15487</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5159; 18597</t>
+          <t>5552; 18368</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4665; 17052</t>
+          <t>4435; 17407</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8118; 24249</t>
+          <t>7139; 23718</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6411; 22387</t>
+          <t>6491; 21464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8818; 29745</t>
+          <t>8794; 28194</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14997</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9516; 27268</t>
+          <t>9282; 27131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4140; 17069</t>
+          <t>3496; 16667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6833</t>
+          <t>0; 7430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3308; 23394</t>
+          <t>6808; 22456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2014; 12133</t>
+          <t>2066; 12932</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1939; 11323</t>
+          <t>1925; 10817</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>649; 6056</t>
+          <t>666; 6205</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14086; 32751</t>
+          <t>13884; 34059</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6887; 21963</t>
+          <t>7183; 22955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6508</t>
+          <t>0; 6847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3976; 24677</t>
+          <t>8772; 25265</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>28620</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12034; 30106</t>
+          <t>12389; 30463</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6402; 19831</t>
+          <t>6816; 20679</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4000; 15904</t>
+          <t>4069; 16191</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8552; 25664</t>
+          <t>8872; 26847</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8683; 26047</t>
+          <t>9358; 26533</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4850; 20375</t>
+          <t>4855; 19225</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2170; 12527</t>
+          <t>2732; 13096</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4349; 18077</t>
+          <t>6923; 21589</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23856; 48930</t>
+          <t>24122; 48907</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14475; 33383</t>
+          <t>14021; 33439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8768; 24243</t>
+          <t>8424; 25107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14734; 37404</t>
+          <t>19733; 42319</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27805</t>
+          <t>29248</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1838; 10735</t>
+          <t>1767; 10554</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3109; 14679</t>
+          <t>3676; 14630</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2489; 14032</t>
+          <t>2343; 13722</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4949; 19898</t>
+          <t>5030; 19315</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4170; 18050</t>
+          <t>4129; 17720</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4355; 16843</t>
+          <t>4278; 16353</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3245; 14953</t>
+          <t>3159; 14727</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10754; 26676</t>
+          <t>12352; 27589</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7935; 23965</t>
+          <t>7291; 23289</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10576; 27322</t>
+          <t>10684; 26878</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7551; 24138</t>
+          <t>8049; 23399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18914; 40401</t>
+          <t>20596; 42520</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7653</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>882; 10155</t>
+          <t>876; 10406</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6445</t>
+          <t>0; 6540</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1994; 15123</t>
+          <t>2140; 13688</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 17821</t>
+          <t>0; 15674</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8715; 25023</t>
+          <t>8975; 24914</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10777; 28395</t>
+          <t>11030; 28662</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5964; 19759</t>
+          <t>6599; 22018</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1892; 8807</t>
+          <t>1946; 9557</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10914; 28919</t>
+          <t>11997; 31376</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12640; 30975</t>
+          <t>12615; 31116</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10260; 30467</t>
+          <t>10962; 29528</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3278; 21419</t>
+          <t>3205; 18638</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53459</t>
+          <t>58168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>49144</t>
+          <t>52845</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102603</t>
+          <t>111013</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>41614; 71779</t>
+          <t>41272; 73993</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32033; 59054</t>
+          <t>32756; 59347</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21782; 45872</t>
+          <t>19749; 43481</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37181; 75000</t>
+          <t>42560; 77962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>42381; 73512</t>
+          <t>42415; 72815</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42318; 70126</t>
+          <t>43349; 74654</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27715; 54561</t>
+          <t>27860; 53809</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36399; 65065</t>
+          <t>40902; 68232</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>90524; 133159</t>
+          <t>92469; 136615</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80973; 122999</t>
+          <t>81237; 122882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54763; 89397</t>
+          <t>55921; 89672</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>80477; 128010</t>
+          <t>89718; 133201</t>
         </is>
       </c>
     </row>
